--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008428503609948769</v>
       </c>
       <c r="C2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>23229194</v>
+        <v>4361966</v>
       </c>
       <c r="L2" t="n">
-        <v>13840454</v>
+        <v>2337683</v>
       </c>
       <c r="M2" t="n">
-        <v>3445555</v>
+        <v>501446</v>
       </c>
       <c r="N2" t="n">
-        <v>184274</v>
+        <v>18976</v>
       </c>
       <c r="O2" t="n">
-        <v>2057718</v>
+        <v>298846</v>
       </c>
       <c r="P2" t="n">
-        <v>777419</v>
+        <v>116125</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999950528144836</v>
+        <v>0.9999827146530151</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9198663234710693</v>
+        <v>0.8460901379585266</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8275771737098694</v>
+        <v>0.7022061944007874</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7973494529724121</v>
+        <v>0.6287062168121338</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4476450979709625</v>
+        <v>0.130609542131424</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8214790821075439</v>
+        <v>0.6708434820175171</v>
       </c>
       <c r="W2" t="n">
-        <v>0.89534592628479</v>
+        <v>0.8082815408706665</v>
       </c>
       <c r="X2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="AG2" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AH2" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AI2" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565606117248535</v>
+        <v>0.9563109874725342</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112661480903625</v>
+        <v>0.9112939834594727</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580878376960754</v>
+        <v>0.8580310344696045</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6623296141624451</v>
+        <v>0.6617932319641113</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020044803619385</v>
+        <v>0.9019097685813904</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -795,127 +795,127 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>23229194</v>
+        <v>4361966</v>
       </c>
       <c r="E3" t="n">
-        <v>1886267</v>
+        <v>644056</v>
       </c>
       <c r="F3" t="n">
-        <v>23135</v>
+        <v>10110</v>
       </c>
       <c r="G3" t="n">
-        <v>2797</v>
+        <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>1111</v>
+        <v>414</v>
       </c>
       <c r="I3" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>50082954</v>
+        <v>10016513</v>
       </c>
       <c r="K3" t="n">
-        <v>54481861</v>
+        <v>10518554</v>
       </c>
       <c r="L3" t="n">
-        <v>62443213</v>
+        <v>12064801</v>
       </c>
       <c r="M3" t="n">
-        <v>76110998</v>
+        <v>15100043</v>
       </c>
       <c r="N3" t="n">
-        <v>80974975</v>
+        <v>16114030</v>
       </c>
       <c r="O3" t="n">
-        <v>78654958</v>
+        <v>15673416</v>
       </c>
       <c r="P3" t="n">
-        <v>80590545</v>
+        <v>16108663</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9239000678062439</v>
+        <v>0.869337797164917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8480059504508972</v>
+        <v>0.7141393423080444</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7391839027404785</v>
+        <v>0.5372142791748047</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4134976863861084</v>
+        <v>0.2125971913337708</v>
       </c>
       <c r="V3" t="n">
-        <v>0.808258593082428</v>
+        <v>0.5864877104759216</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8042945265769958</v>
+        <v>0.6004612445831299</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="Z3" t="n">
-        <v>989932</v>
+        <v>198330</v>
       </c>
       <c r="AA3" t="n">
-        <v>42706</v>
+        <v>8575</v>
       </c>
       <c r="AB3" t="n">
-        <v>33970</v>
+        <v>6824</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50083110</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>55412140</v>
+        <v>11092567</v>
       </c>
       <c r="AG3" t="n">
-        <v>63880556</v>
+        <v>12766203</v>
       </c>
       <c r="AH3" t="n">
-        <v>76325582</v>
+        <v>15263782</v>
       </c>
       <c r="AI3" t="n">
-        <v>81051985</v>
+        <v>16210177</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78852750</v>
+        <v>15770083</v>
       </c>
       <c r="AK3" t="n">
-        <v>80615145</v>
+        <v>16122953</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575626254081726</v>
+        <v>0.9573889374732971</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100250601768494</v>
+        <v>0.9100300669670105</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576043844223022</v>
+        <v>0.8572698831558228</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618287563323975</v>
+        <v>0.6612964868545532</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016448855400085</v>
+        <v>0.9016017913818359</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1915513</v>
+        <v>751441</v>
       </c>
       <c r="E4" t="n">
-        <v>13840454</v>
+        <v>2337683</v>
       </c>
       <c r="F4" t="n">
-        <v>512635</v>
+        <v>160930</v>
       </c>
       <c r="G4" t="n">
-        <v>19875</v>
+        <v>10591</v>
       </c>
       <c r="H4" t="n">
-        <v>30720</v>
+        <v>11924</v>
       </c>
       <c r="I4" t="n">
-        <v>1976</v>
+        <v>855</v>
       </c>
       <c r="J4" t="n">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="K4" t="n">
-        <v>2023599</v>
+        <v>793473</v>
       </c>
       <c r="L4" t="n">
-        <v>2883611</v>
+        <v>991372</v>
       </c>
       <c r="M4" t="n">
-        <v>875706</v>
+        <v>296138</v>
       </c>
       <c r="N4" t="n">
-        <v>227378</v>
+        <v>126312</v>
       </c>
       <c r="O4" t="n">
-        <v>447176</v>
+        <v>146632</v>
       </c>
       <c r="P4" t="n">
-        <v>90870</v>
+        <v>27544</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999975562095642</v>
+        <v>0.9999913573265076</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9218787550926208</v>
+        <v>0.8575564622879028</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8376670479774475</v>
+        <v>0.7081224918365479</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7671657800674438</v>
+        <v>0.5793704986572266</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4298943877220154</v>
+        <v>0.1618104726076126</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8148152828216553</v>
+        <v>0.6258358955383301</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8473812937736511</v>
+        <v>0.6890423893928528</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1020717</v>
+        <v>204872</v>
       </c>
       <c r="Z4" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AA4" t="n">
-        <v>414267</v>
+        <v>82914</v>
       </c>
       <c r="AB4" t="n">
-        <v>27445</v>
+        <v>5508</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1093320</v>
+        <v>219460</v>
       </c>
       <c r="AG4" t="n">
-        <v>1446268</v>
+        <v>289970</v>
       </c>
       <c r="AH4" t="n">
-        <v>661122</v>
+        <v>132399</v>
       </c>
       <c r="AI4" t="n">
-        <v>150368</v>
+        <v>30165</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249384</v>
+        <v>49965</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570613503456116</v>
+        <v>0.9568496942520142</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106451869010925</v>
+        <v>0.9106615781784058</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578459620475769</v>
+        <v>0.8576502799987793</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620790362358093</v>
+        <v>0.6615447402000427</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018246531486511</v>
+        <v>0.901755690574646</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>66779</v>
+        <v>27401</v>
       </c>
       <c r="E5" t="n">
-        <v>851016</v>
+        <v>301223</v>
       </c>
       <c r="F5" t="n">
-        <v>3445555</v>
+        <v>501446</v>
       </c>
       <c r="G5" t="n">
-        <v>81343</v>
+        <v>40428</v>
       </c>
       <c r="H5" t="n">
-        <v>204378</v>
+        <v>57884</v>
       </c>
       <c r="I5" t="n">
-        <v>12217</v>
+        <v>5029</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1913346</v>
+        <v>655607</v>
       </c>
       <c r="L5" t="n">
-        <v>2480722</v>
+        <v>935744</v>
       </c>
       <c r="M5" t="n">
-        <v>1215741</v>
+        <v>431973</v>
       </c>
       <c r="N5" t="n">
-        <v>261373</v>
+        <v>70282</v>
       </c>
       <c r="O5" t="n">
-        <v>488148</v>
+        <v>210706</v>
       </c>
       <c r="P5" t="n">
-        <v>189166</v>
+        <v>77268</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999980926513672</v>
+        <v>0.9999933242797852</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9517815113067627</v>
+        <v>0.9112605452537537</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9342992901802063</v>
+        <v>0.8819863200187683</v>
       </c>
       <c r="T5" t="n">
-        <v>0.974384605884552</v>
+        <v>0.9554116129875183</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9940139055252075</v>
+        <v>0.9879608750343323</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9885444641113281</v>
+        <v>0.9781171679496765</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9965702295303345</v>
+        <v>0.9935814738273621</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40062</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>425133</v>
+        <v>85383</v>
       </c>
       <c r="AA5" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AB5" t="n">
-        <v>49729</v>
+        <v>9974</v>
       </c>
       <c r="AC5" t="n">
-        <v>145659</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1066983</v>
+        <v>213804</v>
       </c>
       <c r="AG5" t="n">
-        <v>1468497</v>
+        <v>294510</v>
       </c>
       <c r="AH5" t="n">
-        <v>663748</v>
+        <v>133227</v>
       </c>
       <c r="AI5" t="n">
-        <v>150705</v>
+        <v>30232</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250399</v>
+        <v>50139</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973541259765625</v>
+        <v>0.9734675884246826</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964300811290741</v>
+        <v>0.9642073512077332</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983773410320282</v>
+        <v>0.9837334752082825</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963125586509705</v>
+        <v>0.9963013529777527</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938787817955017</v>
+        <v>0.9938697814941406</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983751177787781</v>
+        <v>0.998373806476593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>40795</v>
+        <v>14279</v>
       </c>
       <c r="E6" t="n">
-        <v>100257</v>
+        <v>20506</v>
       </c>
       <c r="F6" t="n">
-        <v>78992</v>
+        <v>25726</v>
       </c>
       <c r="G6" t="n">
-        <v>184274</v>
+        <v>18976</v>
       </c>
       <c r="H6" t="n">
-        <v>38783</v>
+        <v>8999</v>
       </c>
       <c r="I6" t="n">
-        <v>2533</v>
+        <v>771</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32262</v>
+        <v>6482</v>
       </c>
       <c r="Z6" t="n">
-        <v>26748</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>54395</v>
+        <v>10913</v>
       </c>
       <c r="AB6" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AC6" t="n">
-        <v>34895</v>
+        <v>6990</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>418</v>
+        <v>334</v>
       </c>
       <c r="E7" t="n">
-        <v>43915</v>
+        <v>24419</v>
       </c>
       <c r="F7" t="n">
-        <v>252678</v>
+        <v>95191</v>
       </c>
       <c r="G7" t="n">
-        <v>117016</v>
+        <v>69869</v>
       </c>
       <c r="H7" t="n">
-        <v>2057718</v>
+        <v>298846</v>
       </c>
       <c r="I7" t="n">
-        <v>74108</v>
+        <v>20880</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4050</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148103</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37897</v>
+        <v>7593</v>
       </c>
       <c r="AC7" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="D8" t="n">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>2156</v>
+        <v>1168</v>
       </c>
       <c r="F8" t="n">
-        <v>8266</v>
+        <v>4181</v>
       </c>
       <c r="G8" t="n">
-        <v>6347</v>
+        <v>4406</v>
       </c>
       <c r="H8" t="n">
-        <v>172184</v>
+        <v>67411</v>
       </c>
       <c r="I8" t="n">
-        <v>777419</v>
+        <v>116125</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
